--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNew.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNew.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418921CA-1A2F-4A2C-BB07-803687A48035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="120" windowWidth="16160" windowHeight="8510"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>数据日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -135,10 +136,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>货币市场基金标识</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>其他产品标识1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -168,13 +165,24 @@
   </si>
   <si>
     <t>增信形式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>货币市场基金或现金管理类产品</t>
+  </si>
+  <si>
+    <t>跨境理财通标识</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以财产权信托名义开展的资金信托标识</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -266,7 +274,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -341,6 +349,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -376,6 +401,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -551,16 +593,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AO1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="14.36328125" customWidth="1"/>
-    <col min="14" max="14" width="22.6328125" customWidth="1"/>
-    <col min="25" max="25" width="17.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.33203125" customWidth="1"/>
+    <col min="14" max="14" width="22.6640625" customWidth="1"/>
+    <col min="25" max="25" width="17.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -652,31 +694,37 @@
         <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
-        <v>38</v>
+      <c r="AN1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -687,9 +735,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -698,9 +746,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNew.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/PbcPrdBaseinfoSubNew.xlsx
@@ -1,23 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24701"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418921CA-1A2F-4A2C-BB07-803687A48035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="30940" windowHeight="16900"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621" concurrentCalc="0"/>
+  <calcPr calcId="152511" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t>数据日期</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -133,14 +132,6 @@
   </si>
   <si>
     <t>收益权转让产品标识</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他产品标识1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他产品标识2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -182,7 +173,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -274,7 +265,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -349,23 +340,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -401,23 +375,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -593,16 +550,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AO1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AM1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="8" max="8" width="14.33203125" customWidth="1"/>
-    <col min="14" max="14" width="22.6640625" customWidth="1"/>
-    <col min="25" max="25" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.36328125" customWidth="1"/>
+    <col min="14" max="14" width="22.6328125" customWidth="1"/>
+    <col min="25" max="25" width="17.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
@@ -694,37 +651,31 @@
         <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -735,9 +686,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -746,9 +697,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
